--- a/data/trans_dic/IP31B_R_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP31B_R_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>48,21%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35,69; 60,78</t>
+          <t>40,06; 61,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44,06; 65,04</t>
+          <t>34,37; 55,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42,5; 59,22</t>
+          <t>40,78; 55,73</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>46,03%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,49; 76,42</t>
+          <t>39,11; 57,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41,15; 60,32</t>
+          <t>33,58; 51,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43,45; 67,58</t>
+          <t>39,79; 53,0</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,46%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33,43; 54,14</t>
+          <t>32,69; 52,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33,98; 54,56</t>
+          <t>34,31; 54,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,73; 51,15</t>
+          <t>36,46; 50,82</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,23; 36,08</t>
+          <t>11,73; 34,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,91; 34,18</t>
+          <t>16,86; 35,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,82; 32,72</t>
+          <t>17,17; 32,07</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,84</t>
+          <t>0,0; 6,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,16</t>
+          <t>0,0; 9,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,85</t>
+          <t>0,0; 4,79</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>60,31%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44,9; 67,28</t>
+          <t>55,13; 76,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>55,96; 77,0</t>
+          <t>42,79; 65,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>54,73; 70,34</t>
+          <t>52,49; 68,56</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>30,99%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,18; 35,52</t>
+          <t>27,17; 43,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28,07; 45,24</t>
+          <t>20,87; 33,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26,96; 38,71</t>
+          <t>26,07; 37,02</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,88; 19,12</t>
+          <t>8,7; 17,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,91; 18,24</t>
+          <t>8,94; 20,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,97; 17,11</t>
+          <t>9,92; 17,15</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>31,57%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>29,68; 43,52</t>
+          <t>29,95; 36,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>31,59; 39,0</t>
+          <t>26,9; 33,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31,73; 39,02</t>
+          <t>29,32; 34,05</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33362</t>
+          <t>30734</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>40503</t>
+          <t>24799</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73865</t>
+          <t>55534</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25481; 43394</t>
+          <t>24144; 36885</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>32869; 48521</t>
+          <t>18875; 30578</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>62051; 86463</t>
+          <t>46973; 64190</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>60</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>66680</t>
+          <t>55968</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>63169</t>
+          <t>41566</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>129849</t>
+          <t>97534</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>47411; 94148</t>
+          <t>44838; 65906</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>51862; 76026</t>
+          <t>32648; 50156</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>108274; 168413</t>
+          <t>84308; 112305</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>40</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24548</t>
+          <t>24600</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28070</t>
+          <t>23824</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52619</t>
+          <t>48424</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18568; 30075</t>
+          <t>18733; 30243</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21962; 35265</t>
+          <t>18567; 29381</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44142; 61470</t>
+          <t>40623; 56620</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>18105</t>
+          <t>14823</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15654</t>
+          <t>17586</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33759</t>
+          <t>32409</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12502; 24751</t>
+          <t>7886; 23480</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8522; 24455</t>
+          <t>11676; 24577</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23574; 45850</t>
+          <t>23431; 43774</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>472</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>619</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1090</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2340</t>
+          <t>0; 2442</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3323</t>
+          <t>0; 3515</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3632</t>
+          <t>0; 3587</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>41</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>24798</t>
+          <t>31183</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>36073</t>
+          <t>23993</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>60870</t>
+          <t>55177</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19886; 29797</t>
+          <t>26028; 36127</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>30096; 41410</t>
+          <t>18951; 28932</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>53675; 68983</t>
+          <t>48029; 62731</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>51</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>34291</t>
+          <t>48232</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>54827</t>
+          <t>32674</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>89118</t>
+          <t>80906</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>26118; 43797</t>
+          <t>37932; 60945</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>43246; 69703</t>
+          <t>25356; 41064</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>74790; 107383</t>
+          <t>68082; 96668</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>17366</t>
+          <t>19846</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>20266</t>
+          <t>18742</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>37632</t>
+          <t>38589</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>11427; 24607</t>
+          <t>13672; 27687</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>13741; 28117</t>
+          <t>12330; 28200</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>28184; 48393</t>
+          <t>29275; 50609</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>289</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>219727</t>
+          <t>225858</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>259149</t>
+          <t>183803</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>478876</t>
+          <t>409662</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>192703; 282508</t>
+          <t>204522; 250878</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>233608; 288414</t>
+          <t>165303; 203868</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>440688; 541957</t>
+          <t>380431; 441822</t>
         </is>
       </c>
     </row>
